--- a/词典.xlsx
+++ b/词典.xlsx
@@ -7,7 +7,7 @@
     <workbookView windowWidth="21600" windowHeight="9555"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>层级</t>
   </si>
@@ -38,6 +38,9 @@
     <t>分词词典</t>
   </si>
   <si>
+    <t>扩词</t>
+  </si>
+  <si>
     <t>形式层</t>
   </si>
   <si>
@@ -47,12 +50,18 @@
     <t>产品形态、产品外观</t>
   </si>
   <si>
+    <t>造型、外观设计、产品设计</t>
+  </si>
+  <si>
     <t>色彩、材质与饰面</t>
   </si>
   <si>
     <t>色彩、材质、饰面</t>
   </si>
   <si>
+    <t>线条、风格</t>
+  </si>
+  <si>
     <t>流程层</t>
   </si>
   <si>
@@ -62,50 +71,83 @@
     <t>工业设计中心、设计机构、工业设计示范园区、设计创新智库、设计平台</t>
   </si>
   <si>
+    <t>产业园区、工业园区</t>
+  </si>
+  <si>
     <t>设计人力</t>
   </si>
   <si>
     <t>设计师、设计人员、设计团队</t>
   </si>
   <si>
+    <t>设计者</t>
+  </si>
+  <si>
     <t>管理与方法</t>
   </si>
   <si>
     <t>设计管理、设计流程、设计标准、设计组织、设计评价、设计方法、设计思维</t>
   </si>
   <si>
+    <t>设计规范</t>
+  </si>
+  <si>
     <t>外部协同</t>
   </si>
   <si>
     <t>设计合作、协同设计、开放设计、产业链协同</t>
   </si>
   <si>
+    <t>联合开发、供应链协同、资源整合、价值链协同</t>
+  </si>
+  <si>
     <t>资源投入</t>
   </si>
   <si>
     <t>设计投入、设计费用</t>
   </si>
   <si>
+    <t>研发经费、研发投入</t>
+  </si>
+  <si>
     <t>战略层</t>
   </si>
   <si>
     <t>设计战略</t>
   </si>
   <si>
-    <t xml:space="preserve">设计战略、设计驱动、设计驱动型创新、设计主导
+    <t xml:space="preserve">以设计为核心、设计战略、设计驱动、设计驱动型创新、设计主导
 </t>
   </si>
   <si>
+    <t>设计赋能</t>
+  </si>
+  <si>
     <t>意义创新</t>
   </si>
   <si>
     <t>意义创新、产品意义、产品语言、文化符号、产品语意、情感价值、社会文化、身份认同、生活方式</t>
   </si>
   <si>
+    <t>情感感知、人文精神、价值观、创造、创新能力、革新</t>
+  </si>
+  <si>
     <t>诠释网络与设计话语</t>
   </si>
   <si>
-    <t>设计网络、设计创新网络、外部设计师、艺术家、设计顾问、跨行业企业、设计对话、设计论坛</t>
+    <t>设计网络、设计创新网络、外部设计师、艺术家、设计顾问、设计对话、设计论坛</t>
+  </si>
+  <si>
+    <t>网络化协作、行业交流、制造商、媒体</t>
+  </si>
+  <si>
+    <t>注：</t>
+  </si>
+  <si>
+    <t>注：为区分语义场、规避文本识别噪音，词典构建过程中统一剔除四类无关混淆词汇：
+①机械土建工程类术语：设计产能、设计压力、设计温度、设计流量、设计参数、设计工况、设计寿命、设计变更、设计图纸、工程设计、勘察设计、设计院、初步设计、施工图设计、设计资质；
+②企业治理虚化表述：顶层设计、制度设计、机制设计、股权设计、薪酬设计；
+③无关金融词汇：联名担保、联名账户。同时词典不单独收录单字 “设计”，仅收录二字及以上专业复合词汇，依靠固定搭配限定工业设计语境，降低跨维度误识别概率。</t>
   </si>
 </sst>
 </file>
@@ -128,6 +170,7 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -742,18 +785,34 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1280,123 +1339,169 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="9.02654867256637" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="15.9380530973451" customWidth="1"/>
-    <col min="2" max="2" width="34.6548672566372" customWidth="1"/>
-    <col min="3" max="3" width="105.469026548673" customWidth="1"/>
+    <col min="1" max="1" width="8.23893805309734" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20.1858407079646" style="1" customWidth="1"/>
+    <col min="3" max="3" width="88.6814159292035" style="1" customWidth="1"/>
+    <col min="4" max="4" width="60.141592920354" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9.02654867256637" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:4">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="C2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
+    <row r="3" s="1" customFormat="1" spans="1:4">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>10</v>
+    <row r="4" s="1" customFormat="1" spans="1:4">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>12</v>
+    <row r="5" s="1" customFormat="1" spans="1:4">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>14</v>
+    <row r="6" s="1" customFormat="1" spans="1:4">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
+    <row r="7" s="1" customFormat="1" spans="1:4">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>18</v>
+    <row r="8" s="1" customFormat="1" spans="1:4">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1" spans="1:3">
-      <c r="A9" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>21</v>
+    <row r="9" s="1" customFormat="1" ht="27" spans="1:4">
+      <c r="A9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>23</v>
+    <row r="10" s="1" customFormat="1" spans="1:4">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>25</v>
-      </c>
+    <row r="11" s="1" customFormat="1" spans="1:4">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="86" customHeight="1" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
+    <mergeCell ref="B13:D13"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A8"/>
     <mergeCell ref="A9:A11"/>
